--- a/modelos/MODELO_SI.xlsx
+++ b/modelos/MODELO_SI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f836c1a7bcc1db56/Área de Trabalho/vs/atv002/OPERACAO_BACKEND/modelos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinig\OneDrive\Área de Trabalho\vs\atv002\OPERACAO_BACKEND\modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF5CBAD8-DC8F-494D-842D-9E6BB92D9660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525ED51F-258E-4D1D-AEDF-EA42530E8D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5460" yWindow="3360" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -605,7 +605,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -622,125 +622,115 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -752,10 +742,19 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -771,49 +770,66 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="justify" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1199,61 +1215,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="42"/>
-      <c r="B1" s="31"/>
-      <c r="C1" s="29" t="s">
+      <c r="A1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="22" t="s">
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="36" t="s">
+      <c r="H1" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="31"/>
+      <c r="I1" s="40"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="33"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="44"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="51"/>
-      <c r="I3" s="52"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="50" t="s">
+      <c r="B4" s="14"/>
+      <c r="C4" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="14"/>
       <c r="G4" s="46" t="s">
         <v>7</v>
       </c>
@@ -1261,103 +1277,103 @@
       <c r="I4" s="48"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="40"/>
-      <c r="B5" s="41"/>
+      <c r="A5" s="37"/>
+      <c r="B5" s="38"/>
       <c r="C5" s="49" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="27" t="s">
+      <c r="F5" s="6"/>
+      <c r="G5" s="53" t="s">
         <v>9</v>
       </c>
       <c r="H5" s="8"/>
-      <c r="I5" s="9"/>
+      <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="33" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="28" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="33" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="8"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="25" t="s">
+      <c r="F6" s="6"/>
+      <c r="G6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="18"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="32" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="8"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="37" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="32" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="27" t="s">
+      <c r="F7" s="6"/>
+      <c r="G7" s="53" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="8"/>
-      <c r="I7" s="9"/>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="25" t="s">
+      <c r="B8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="25" t="s">
+      <c r="E8" s="21"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="32" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="16" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="57" t="s">
+      <c r="E9" s="21"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="17"/>
-      <c r="I9" s="18"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="18"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="58"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -1365,83 +1381,83 @@
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
-      <c r="I11" s="9"/>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="25" t="s">
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="18"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="24" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="15" t="s">
+      <c r="E13" s="6"/>
+      <c r="F13" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
-      <c r="I13" s="9"/>
+      <c r="I13" s="6"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="25" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="18"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="24" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="15" t="s">
+      <c r="E15" s="6"/>
+      <c r="F15" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
-      <c r="I15" s="9"/>
+      <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="18"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="61"/>
+      <c r="A17" s="19"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -1449,132 +1465,132 @@
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
-      <c r="I17" s="9"/>
+      <c r="I17" s="6"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="25" t="s">
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="18"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="24" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="15" t="s">
+      <c r="E19" s="6"/>
+      <c r="F19" s="24" t="s">
         <v>33</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
-      <c r="I19" s="9"/>
+      <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="59" t="s">
+      <c r="A20" s="15" t="s">
         <v>34</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="20" t="s">
+      <c r="D20" s="6"/>
+      <c r="E20" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="20" t="s">
+      <c r="F20" s="60"/>
+      <c r="G20" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="H20" s="21"/>
+      <c r="H20" s="60"/>
       <c r="I20" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="10" t="s">
+      <c r="B21" s="61"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="39" t="s">
+      <c r="F21" s="61"/>
+      <c r="G21" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="H21" s="11"/>
-      <c r="I21" s="34" t="s">
+      <c r="H21" s="61"/>
+      <c r="I21" s="56" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="35"/>
+      <c r="A22" s="62"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="65"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="51" t="s">
         <v>39</v>
       </c>
       <c r="B23" s="8"/>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D23" s="8"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="53" t="s">
+      <c r="E23" s="6"/>
+      <c r="F23" s="34" t="s">
         <v>41</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
-      <c r="I23" s="9"/>
+      <c r="I23" s="6"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="17" t="s">
         <v>42</v>
       </c>
       <c r="B24" s="11"/>
-      <c r="C24" s="60"/>
-      <c r="D24" s="55"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="10"/>
       <c r="E24" s="11"/>
-      <c r="F24" s="54" t="s">
+      <c r="F24" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="G24" s="55"/>
-      <c r="H24" s="55"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
       <c r="I24" s="11"/>
     </row>
     <row r="25" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
+      <c r="B25" s="14"/>
       <c r="C25" s="12"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="14"/>
       <c r="F25" s="12"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="14"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="38" t="s">
+      <c r="A26" s="7" t="s">
         <v>44</v>
       </c>
       <c r="B26" s="8"/>
@@ -1584,10 +1600,10 @@
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
-      <c r="I26" s="9"/>
+      <c r="I26" s="6"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="16" t="s">
         <v>45</v>
       </c>
       <c r="B27" s="8"/>
@@ -1597,10 +1613,10 @@
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
-      <c r="I27" s="9"/>
+      <c r="I27" s="6"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="38" t="s">
+      <c r="A28" s="7" t="s">
         <v>46</v>
       </c>
       <c r="B28" s="8"/>
@@ -1610,10 +1626,10 @@
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
-      <c r="I28" s="9"/>
+      <c r="I28" s="6"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="16" t="s">
         <v>47</v>
       </c>
       <c r="B29" s="8"/>
@@ -1623,10 +1639,10 @@
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
-      <c r="I29" s="9"/>
+      <c r="I29" s="6"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="38" t="s">
+      <c r="A30" s="7" t="s">
         <v>48</v>
       </c>
       <c r="B30" s="8"/>
@@ -1636,10 +1652,10 @@
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
-      <c r="I30" s="9"/>
+      <c r="I30" s="6"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="16" t="s">
         <v>49</v>
       </c>
       <c r="B31" s="8"/>
@@ -1649,10 +1665,10 @@
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
-      <c r="I31" s="9"/>
+      <c r="I31" s="6"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="38" t="s">
+      <c r="A32" s="7" t="s">
         <v>50</v>
       </c>
       <c r="B32" s="8"/>
@@ -1662,34 +1678,34 @@
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
-      <c r="I32" s="9"/>
+      <c r="I32" s="6"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="17" t="s">
         <v>37</v>
       </c>
       <c r="B33" s="11"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="55"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="12"/>
-      <c r="B34" s="13"/>
+      <c r="B34" s="14"/>
       <c r="C34" s="12"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="14"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="38" t="s">
+      <c r="A35" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B35" s="8"/>
@@ -1699,34 +1715,34 @@
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
-      <c r="I35" s="9"/>
+      <c r="I35" s="6"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="17" t="s">
         <v>52</v>
       </c>
       <c r="B36" s="11"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
-      <c r="B37" s="13"/>
+      <c r="B37" s="14"/>
       <c r="C37" s="12"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="14"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="38" t="s">
+      <c r="A38" s="7" t="s">
         <v>53</v>
       </c>
       <c r="B38" s="8"/>
@@ -1736,32 +1752,32 @@
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
-      <c r="I38" s="9"/>
+      <c r="I38" s="6"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
+      <c r="A39" s="17"/>
       <c r="B39" s="11"/>
-      <c r="C39" s="56"/>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
       <c r="I39" s="11"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
-      <c r="B40" s="13"/>
+      <c r="B40" s="14"/>
       <c r="C40" s="12"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="14"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="38" t="s">
+      <c r="A41" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B41" s="8"/>
@@ -1771,71 +1787,71 @@
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
-      <c r="I41" s="9"/>
+      <c r="I41" s="6"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="9"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="6"/>
       <c r="D42" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E42" s="26"/>
-      <c r="F42" s="9"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="6"/>
       <c r="G42" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="H42" s="26"/>
-      <c r="I42" s="9"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="6"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B43" s="26"/>
-      <c r="C43" s="9"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="6"/>
       <c r="D43" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E43" s="26"/>
-      <c r="F43" s="9"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6"/>
       <c r="G43" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H43" s="26"/>
-      <c r="I43" s="9"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="6"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="28" t="s">
         <v>59</v>
       </c>
       <c r="B44" s="8"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="26"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="5"/>
       <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="38" t="s">
+      <c r="F44" s="6"/>
+      <c r="G44" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H44" s="26" t="s">
+      <c r="H44" s="5" t="s">
         <v>61</v>
       </c>
       <c r="I44" s="11"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="28" t="s">
         <v>58</v>
       </c>
       <c r="B45" s="8"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="26"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="5"/>
       <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="35"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="25"/>
       <c r="H45" s="12"/>
-      <c r="I45" s="13"/>
+      <c r="I45" s="14"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="45" t="s">
@@ -1848,40 +1864,40 @@
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
-      <c r="I46" s="9"/>
+      <c r="I46" s="6"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="45" t="s">
         <v>63</v>
       </c>
       <c r="B47" s="11"/>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="D47" s="18"/>
-      <c r="E47" s="19" t="s">
+      <c r="D47" s="22"/>
+      <c r="E47" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="F47" s="18"/>
-      <c r="G47" s="19" t="s">
+      <c r="F47" s="22"/>
+      <c r="G47" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="H47" s="17"/>
-      <c r="I47" s="18"/>
+      <c r="H47" s="21"/>
+      <c r="I47" s="22"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="18"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="21"/>
+      <c r="I48" s="22"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="38" t="s">
+      <c r="A49" s="7" t="s">
         <v>67</v>
       </c>
       <c r="B49" s="8"/>
@@ -1891,129 +1907,96 @@
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
-      <c r="I49" s="9"/>
+      <c r="I49" s="6"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="28" t="s">
         <v>59</v>
       </c>
       <c r="B50" s="8"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="26"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="5"/>
       <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="38" t="s">
+      <c r="F50" s="6"/>
+      <c r="G50" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H50" s="26" t="s">
+      <c r="H50" s="5" t="s">
         <v>61</v>
       </c>
       <c r="I50" s="11"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="28" t="s">
         <v>58</v>
       </c>
       <c r="B51" s="8"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="26"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="5"/>
       <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="35"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="25"/>
       <c r="H51" s="12"/>
-      <c r="I51" s="13"/>
+      <c r="I51" s="14"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B52" s="26"/>
-      <c r="C52" s="9"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="6"/>
       <c r="D52" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E52" s="26"/>
-      <c r="F52" s="9"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="6"/>
       <c r="G52" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H52" s="26"/>
-      <c r="I52" s="9"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="6"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B53" s="26"/>
-      <c r="C53" s="9"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="6"/>
       <c r="D53" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E53" s="26" t="s">
+      <c r="E53" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F53" s="9"/>
+      <c r="F53" s="6"/>
       <c r="G53" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H53" s="26"/>
-      <c r="I53" s="9"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="103">
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="C33:I34"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C24:E25"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="C36:I37"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="C39:I40"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="H44:I45"/>
-    <mergeCell ref="A24:B25"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="F24:I25"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="E21:F22"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="G21:H22"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="C1:F2"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A39:B40"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="H1:I2"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A38:I38"/>
     <mergeCell ref="A1:B3"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="A47:B48"/>
@@ -2030,7 +2013,6 @@
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="F18:I18"/>
-    <mergeCell ref="H50:I51"/>
     <mergeCell ref="H42:I42"/>
     <mergeCell ref="D45:F45"/>
     <mergeCell ref="A13:E13"/>
@@ -2039,31 +2021,65 @@
     <mergeCell ref="A16:I16"/>
     <mergeCell ref="E43:F43"/>
     <mergeCell ref="A15:E15"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="H44:I45"/>
+    <mergeCell ref="A24:B25"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="F24:I25"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="E21:F22"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="G21:H22"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="C36:I37"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="C39:I40"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="H50:I51"/>
     <mergeCell ref="E42:F42"/>
-    <mergeCell ref="C1:F2"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A39:B40"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="H1:I2"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A36:B37"/>
     <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A19:E19"/>
     <mergeCell ref="G48:I48"/>
     <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A32:I32"/>
     <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="C33:I34"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C24:E25"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="E53:F53"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H50:I51" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/modelos/MODELO_SI.xlsx
+++ b/modelos/MODELO_SI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinig\OneDrive\Área de Trabalho\vs\atv002\OPERACAO_BACKEND\modelos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MarcioOliveira\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525ED51F-258E-4D1D-AEDF-EA42530E8D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F942B9A9-5137-44BE-AE83-9CAF88BA53DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="74">
   <si>
     <t>SI - Solicitação de Intervenção</t>
   </si>
@@ -122,12 +122,6 @@
   </si>
   <si>
     <t>Marcelo Leal</t>
-  </si>
-  <si>
-    <t>Aproveitamento?</t>
-  </si>
-  <si>
-    <t>Inclusão de Serviço?</t>
   </si>
   <si>
     <t xml:space="preserve">Órgãos </t>
@@ -235,17 +229,29 @@
     <t>05/03/26 11:30</t>
   </si>
   <si>
-    <t>A postergação traz risco?</t>
-  </si>
-  <si>
     <t xml:space="preserve">SIM - Equipamento </t>
+  </si>
+  <si>
+    <t>INTERROMPIDA</t>
+  </si>
+  <si>
+    <t>Aproveitamento:</t>
+  </si>
+  <si>
+    <t>Inclusão de Serviço:</t>
+  </si>
+  <si>
+    <t>Acarreta risco de Perdas multiplas:</t>
+  </si>
+  <si>
+    <t>A postergação traz risco:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +283,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -605,7 +618,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -661,10 +674,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -808,10 +817,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -824,11 +829,27 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1205,175 +1226,175 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.3984375" customWidth="1"/>
+    <col min="6" max="6" width="9.296875" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9.59765625" customWidth="1"/>
+    <col min="9" max="9" width="13.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="39"/>
-      <c r="B1" s="40"/>
-      <c r="C1" s="54" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="50" t="s">
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="57" t="s">
+      <c r="H1" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="40"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="43"/>
+      <c r="I1" s="39"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="42"/>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="42"/>
       <c r="H2" s="13"/>
-      <c r="I2" s="44"/>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="43"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="58" t="s">
+      <c r="I2" s="43"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A3" s="42"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="31"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="H3" s="29"/>
+      <c r="I3" s="30"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="51" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="14"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="14"/>
-      <c r="G4" s="46" t="s">
+      <c r="G4" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="47"/>
-      <c r="I4" s="48"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="49" t="s">
+      <c r="H4" s="46"/>
+      <c r="I4" s="47"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A5" s="36"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="6"/>
-      <c r="G5" s="53" t="s">
+      <c r="G5" s="52" t="s">
         <v>9</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
+    <row r="6" spans="1:9">
+      <c r="A6" s="32" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="6"/>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="32" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="6"/>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="22"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+      <c r="H6" s="20"/>
+      <c r="I6" s="21"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="31" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="31" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="53" t="s">
+      <c r="G7" s="52" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
+    <row r="8" spans="1:9" ht="27" customHeight="1">
+      <c r="A8" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="27" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="21"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="27" t="s">
+      <c r="E8" s="20"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="21"/>
-      <c r="I8" s="22"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
+      <c r="H8" s="20"/>
+      <c r="I8" s="21"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="31" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="6"/>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="21"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="23" t="s">
+      <c r="E9" s="20"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="21"/>
-      <c r="I9" s="22"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
+      <c r="H9" s="20"/>
+      <c r="I9" s="21"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="22"/>
-    </row>
-    <row r="11" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="21"/>
+    </row>
+    <row r="11" spans="1:9" ht="52.5" customHeight="1">
+      <c r="A11" s="25"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -1383,81 +1404,81 @@
       <c r="H11" s="8"/>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
+    <row r="12" spans="1:9">
+      <c r="A12" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="27" t="s">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="22"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="21"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="23" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="23" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="27" t="s">
+    <row r="14" spans="1:9">
+      <c r="A14" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="27" t="s">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="22"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="21"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="23" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="23" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
+    <row r="16" spans="1:9">
+      <c r="A16" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="22"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="21"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="18"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -1467,120 +1488,124 @@
       <c r="H17" s="8"/>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+    <row r="18" spans="1:9">
+      <c r="A18" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="27" t="s">
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="22"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="21"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="23" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="6"/>
-      <c r="F19" s="24" t="s">
+      <c r="F19" s="23" t="s">
         <v>33</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="6"/>
     </row>
-    <row r="20" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+    <row r="20" spans="1:9" ht="26.4" customHeight="1">
+      <c r="A20" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="63"/>
+      <c r="C20" s="62" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="63"/>
+      <c r="E20" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="63"/>
+      <c r="G20" s="62" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" s="63"/>
+      <c r="I20" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="51" t="s">
+    </row>
+    <row r="21" spans="1:9" ht="13.8" customHeight="1">
+      <c r="A21" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="F20" s="60"/>
-      <c r="G20" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="H20" s="60"/>
-      <c r="I20" s="3" t="s">
+      <c r="B21" s="65"/>
+      <c r="C21" s="64" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="65"/>
+      <c r="E21" s="64" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="65"/>
+      <c r="G21" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" s="65"/>
+      <c r="I21" s="55" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
+    <row r="22" spans="1:9" ht="36.75" customHeight="1">
+      <c r="A22" s="66"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="24"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="50" t="s">
         <v>37</v>
-      </c>
-      <c r="B21" s="61"/>
-      <c r="C21" s="64"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="61"/>
-      <c r="G21" s="64" t="s">
-        <v>71</v>
-      </c>
-      <c r="H21" s="61"/>
-      <c r="I21" s="56" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="62"/>
-      <c r="B22" s="63"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="63"/>
-      <c r="I22" s="65"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="51" t="s">
-        <v>39</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="6"/>
-      <c r="F23" s="34" t="s">
-        <v>41</v>
+      <c r="F23" s="33" t="s">
+        <v>39</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
       <c r="I23" s="6"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="18"/>
+    <row r="24" spans="1:9">
+      <c r="A24" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="59"/>
+      <c r="C24" s="17"/>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
-      <c r="F24" s="35" t="s">
-        <v>43</v>
+      <c r="F24" s="34" t="s">
+        <v>41</v>
       </c>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
-      <c r="B25" s="14"/>
+    <row r="25" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A25" s="60"/>
+      <c r="B25" s="61"/>
       <c r="C25" s="12"/>
       <c r="D25" s="13"/>
       <c r="E25" s="14"/>
@@ -1589,9 +1614,9 @@
       <c r="H25" s="13"/>
       <c r="I25" s="14"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9">
       <c r="A26" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -1602,9 +1627,9 @@
       <c r="H26" s="8"/>
       <c r="I26" s="6"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9">
       <c r="A27" s="16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -1615,9 +1640,9 @@
       <c r="H27" s="8"/>
       <c r="I27" s="6"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9">
       <c r="A28" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -1628,9 +1653,9 @@
       <c r="H28" s="8"/>
       <c r="I28" s="6"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9">
       <c r="A29" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -1641,9 +1666,9 @@
       <c r="H29" s="8"/>
       <c r="I29" s="6"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9">
       <c r="A30" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -1654,9 +1679,9 @@
       <c r="H30" s="8"/>
       <c r="I30" s="6"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9">
       <c r="A31" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -1667,9 +1692,9 @@
       <c r="H31" s="8"/>
       <c r="I31" s="6"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9">
       <c r="A32" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -1680,11 +1705,11 @@
       <c r="H32" s="8"/>
       <c r="I32" s="6"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="11"/>
+    <row r="33" spans="1:9">
+      <c r="A33" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="59"/>
       <c r="C33" s="9"/>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
@@ -1693,9 +1718,9 @@
       <c r="H33" s="10"/>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="12"/>
-      <c r="B34" s="14"/>
+    <row r="34" spans="1:9">
+      <c r="A34" s="60"/>
+      <c r="B34" s="61"/>
       <c r="C34" s="12"/>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
@@ -1704,9 +1729,9 @@
       <c r="H34" s="13"/>
       <c r="I34" s="14"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9">
       <c r="A35" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -1717,11 +1742,11 @@
       <c r="H35" s="8"/>
       <c r="I35" s="6"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B36" s="11"/>
+    <row r="36" spans="1:9">
+      <c r="A36" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="59"/>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
@@ -1730,9 +1755,9 @@
       <c r="H36" s="10"/>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
-      <c r="B37" s="14"/>
+    <row r="37" spans="1:9">
+      <c r="A37" s="60"/>
+      <c r="B37" s="61"/>
       <c r="C37" s="12"/>
       <c r="D37" s="13"/>
       <c r="E37" s="13"/>
@@ -1741,9 +1766,9 @@
       <c r="H37" s="13"/>
       <c r="I37" s="14"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9">
       <c r="A38" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -1754,9 +1779,11 @@
       <c r="H38" s="8"/>
       <c r="I38" s="6"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="17"/>
-      <c r="B39" s="11"/>
+    <row r="39" spans="1:9">
+      <c r="A39" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="59"/>
       <c r="C39" s="9"/>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
@@ -1765,9 +1792,9 @@
       <c r="H39" s="10"/>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
-      <c r="B40" s="14"/>
+    <row r="40" spans="1:9">
+      <c r="A40" s="60"/>
+      <c r="B40" s="61"/>
       <c r="C40" s="12"/>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
@@ -1776,9 +1803,9 @@
       <c r="H40" s="13"/>
       <c r="I40" s="14"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9">
       <c r="A41" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -1789,43 +1816,43 @@
       <c r="H41" s="8"/>
       <c r="I41" s="6"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9">
       <c r="A42" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="6"/>
       <c r="D42" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="6"/>
       <c r="G42" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9">
       <c r="A43" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="6"/>
       <c r="D43" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="6"/>
       <c r="G43" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="6"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="28" t="s">
-        <v>59</v>
+    <row r="44" spans="1:9">
+      <c r="A44" s="27" t="s">
+        <v>57</v>
       </c>
       <c r="B44" s="8"/>
       <c r="C44" s="6"/>
@@ -1833,29 +1860,29 @@
       <c r="E44" s="8"/>
       <c r="F44" s="6"/>
       <c r="G44" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="28" t="s">
-        <v>58</v>
+    <row r="45" spans="1:9">
+      <c r="A45" s="27" t="s">
+        <v>56</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="6"/>
       <c r="D45" s="5"/>
       <c r="E45" s="8"/>
       <c r="F45" s="6"/>
-      <c r="G45" s="25"/>
+      <c r="G45" s="24"/>
       <c r="H45" s="12"/>
       <c r="I45" s="14"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="45" t="s">
-        <v>62</v>
+    <row r="46" spans="1:9">
+      <c r="A46" s="44" t="s">
+        <v>60</v>
       </c>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -1866,39 +1893,39 @@
       <c r="H46" s="8"/>
       <c r="I46" s="6"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="45" t="s">
+    <row r="47" spans="1:9">
+      <c r="A47" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="11"/>
+      <c r="C47" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D47" s="21"/>
+      <c r="E47" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="36" t="s">
+      <c r="F47" s="21"/>
+      <c r="G47" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="D47" s="22"/>
-      <c r="E47" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="F47" s="22"/>
-      <c r="G47" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="H47" s="21"/>
-      <c r="I47" s="22"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H47" s="20"/>
+      <c r="I47" s="21"/>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="12"/>
       <c r="B48" s="14"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="22"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C48" s="19"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="21"/>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -1909,9 +1936,9 @@
       <c r="H49" s="8"/>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="28" t="s">
-        <v>59</v>
+    <row r="50" spans="1:9">
+      <c r="A50" s="27" t="s">
+        <v>57</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="6"/>
@@ -1919,64 +1946,64 @@
       <c r="E50" s="8"/>
       <c r="F50" s="6"/>
       <c r="G50" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="28" t="s">
-        <v>58</v>
+    <row r="51" spans="1:9">
+      <c r="A51" s="27" t="s">
+        <v>56</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="6"/>
       <c r="D51" s="5"/>
       <c r="E51" s="8"/>
       <c r="F51" s="6"/>
-      <c r="G51" s="25"/>
+      <c r="G51" s="24"/>
       <c r="H51" s="12"/>
       <c r="I51" s="14"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9">
       <c r="A52" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="6"/>
       <c r="D52" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="6"/>
       <c r="G52" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="6"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9">
       <c r="A53" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="6"/>
       <c r="D53" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="103">
+  <mergeCells count="104">
     <mergeCell ref="C1:F2"/>
     <mergeCell ref="F14:I14"/>
     <mergeCell ref="A8:C8"/>
@@ -1997,6 +2024,8 @@
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="A1:B3"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="A47:B48"/>
@@ -2071,7 +2100,6 @@
     <mergeCell ref="H53:I53"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="C33:I34"/>
-    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A27:I27"/>
     <mergeCell ref="A21:B22"/>
     <mergeCell ref="C24:E25"/>
